--- a/recharge/resources/sample/Item.xlsx
+++ b/recharge/resources/sample/Item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -2269,7 +2269,7 @@
         <v>999</v>
       </c>
       <c r="R8">
-        <v>0.003</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:18">
@@ -2313,7 +2313,7 @@
         <v>999</v>
       </c>
       <c r="R9">
-        <v>0.495</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:18">

--- a/recharge/resources/sample/Item.xlsx
+++ b/recharge/resources/sample/Item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -2269,7 +2269,7 @@
         <v>999</v>
       </c>
       <c r="R8">
-        <v>0.05</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:18">
@@ -2313,7 +2313,7 @@
         <v>999</v>
       </c>
       <c r="R9">
-        <v>0.99</v>
+        <v>0.495</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:18">
